--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F5574C-E25C-402D-BC18-B4184B98BB11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB8E918-DDE6-4071-A48C-62F6522783E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15165" yWindow="0" windowWidth="13290" windowHeight="15585" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="6855" yWindow="465" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
   <si>
     <t>source</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>IS_SUPPORTED_BY</t>
+  </si>
+  <si>
+    <t>IS_SUPERSEDED_BY</t>
+  </si>
+  <si>
+    <t>SUPERSEDES</t>
   </si>
 </sst>
 </file>
@@ -430,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -469,6 +475,28 @@
       </c>
       <c r="C3" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB8E918-DDE6-4071-A48C-62F6522783E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6D0A334-C160-4801-BEFD-5B6F29443041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6855" yWindow="465" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="meta-model" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>source</t>
   </si>
@@ -63,6 +63,15 @@
   </si>
   <si>
     <t>SUPERSEDES</t>
+  </si>
+  <si>
+    <t>Business_Driver</t>
+  </si>
+  <si>
+    <t>MOTIVATES</t>
+  </si>
+  <si>
+    <t>IS_MOTIVATED_BY</t>
   </si>
 </sst>
 </file>
@@ -436,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -499,6 +508,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6D0A334-C160-4801-BEFD-5B6F29443041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1B3F70C2-C226-4BD9-94E8-F80C323DA842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6855" yWindow="465" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="1995" yWindow="1380" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
   <si>
     <t>source</t>
   </si>
@@ -72,6 +72,24 @@
   </si>
   <si>
     <t>IS_MOTIVATED_BY</t>
+  </si>
+  <si>
+    <t>HAS_APPLICATION_IMPLICATIONS</t>
+  </si>
+  <si>
+    <t>Application_Driver</t>
+  </si>
+  <si>
+    <t>source_label</t>
+  </si>
+  <si>
+    <t>target_label</t>
+  </si>
+  <si>
+    <t>Business_Conceptual</t>
+  </si>
+  <si>
+    <t>Application_Conceptual</t>
   </si>
 </sst>
 </file>
@@ -445,89 +463,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" t="s">
-        <v>5</v>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{1B3F70C2-C226-4BD9-94E8-F80C323DA842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C53212-F18F-4411-9368-2EECFEAA3C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1995" yWindow="1380" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="19">
   <si>
     <t>source</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Application_Conceptual</t>
+  </si>
+  <si>
+    <t>Business_Capability</t>
   </si>
 </sst>
 </file>
@@ -113,7 +116,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -121,17 +124,292 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{B97C86DB-084A-4C6E-89CC-C827E360EC73}"/>
   </tableStyles>
@@ -144,6 +422,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E12" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E12" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{1E0A4054-BF99-49ED-AC58-444DECF4AD30}" name="relation" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{0018AE30-4EEE-4F1D-A8CD-064A4C284D25}" name="target" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{12343957-196D-4BE2-AD34-9ED5E4F6C16C}" name="target_label" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -463,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -474,143 +766,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="9" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C53212-F18F-4411-9368-2EECFEAA3C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DD2BE9-B497-49AF-A083-06750B8F1148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="1380" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="7590" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="22">
   <si>
     <t>source</t>
   </si>
@@ -93,6 +93,15 @@
   </si>
   <si>
     <t>Business_Capability</t>
+  </si>
+  <si>
+    <t>REQUIRES</t>
+  </si>
+  <si>
+    <t>IS_REQUIRED_BY</t>
+  </si>
+  <si>
+    <t>Skill_Type</t>
   </si>
 </sst>
 </file>
@@ -425,8 +434,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E12" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E12" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E16" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E16" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -755,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -966,6 +975,74 @@
         <v>18</v>
       </c>
       <c r="E12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2DD2BE9-B497-49AF-A083-06750B8F1148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C73E01D-9665-4B4E-960C-FAE59851845A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7590" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
   <si>
     <t>source</t>
   </si>
@@ -102,6 +102,21 @@
   </si>
   <si>
     <t>Skill_Type</t>
+  </si>
+  <si>
+    <t>BELONGS_TO</t>
+  </si>
+  <si>
+    <t>Business_Domain</t>
+  </si>
+  <si>
+    <t>CONTAINS</t>
+  </si>
+  <si>
+    <t>STRATEGIC_OBJECTIVES</t>
+  </si>
+  <si>
+    <t>OBJECTIVE_FOR_BUSINESS_DOMAINS</t>
   </si>
 </sst>
 </file>
@@ -434,8 +449,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E16" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E16" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E22" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -764,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -1043,6 +1058,108 @@
         <v>18</v>
       </c>
       <c r="E16" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>16</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C73E01D-9665-4B4E-960C-FAE59851845A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F60A70D-38E9-4798-8CCA-192509075ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7590" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="29">
   <si>
     <t>source</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>OBJECTIVE_FOR_BUSINESS_DOMAINS</t>
+  </si>
+  <si>
+    <t>Application_Capability</t>
+  </si>
+  <si>
+    <t>Product_Concept</t>
   </si>
 </sst>
 </file>
@@ -449,8 +455,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E22" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E25" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E25" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -779,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -1160,6 +1166,57 @@
         <v>23</v>
       </c>
       <c r="E22" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F60A70D-38E9-4798-8CCA-192509075ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA5D600-4AA1-4BDE-A12D-267D8D1C18CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7590" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="5445" yWindow="2130" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="37">
   <si>
     <t>source</t>
   </si>
@@ -123,6 +123,30 @@
   </si>
   <si>
     <t>Product_Concept</t>
+  </si>
+  <si>
+    <t>Business_Role_Type</t>
+  </si>
+  <si>
+    <t>PROVIDES</t>
+  </si>
+  <si>
+    <t>MEMBERS_OF</t>
+  </si>
+  <si>
+    <t>External_Business_Role_Type</t>
+  </si>
+  <si>
+    <t>RAISES</t>
+  </si>
+  <si>
+    <t>External_Conceptual_Business_Event</t>
+  </si>
+  <si>
+    <t>Conceptual_Business_Event</t>
+  </si>
+  <si>
+    <t>Time_Based_Conceptual_Business_Event</t>
   </si>
 </sst>
 </file>
@@ -455,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E25" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E25" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E30" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E30" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -785,13 +809,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.5703125" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1217,6 +1241,91 @@
         <v>18</v>
       </c>
       <c r="E25" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="9" t="s">
         <v>16</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA5D600-4AA1-4BDE-A12D-267D8D1C18CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4755D47A-C37D-4FD6-A4C3-7EA226D62775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5445" yWindow="2130" windowWidth="21600" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="11460" yWindow="1125" windowWidth="16200" windowHeight="14325" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="44">
   <si>
     <t>source</t>
   </si>
@@ -56,12 +56,6 @@
     <t>Business_Objectives</t>
   </si>
   <si>
-    <t>IS_SUPPORTED_BY</t>
-  </si>
-  <si>
-    <t>IS_SUPERSEDED_BY</t>
-  </si>
-  <si>
     <t>SUPERSEDES</t>
   </si>
   <si>
@@ -71,9 +65,6 @@
     <t>MOTIVATES</t>
   </si>
   <si>
-    <t>IS_MOTIVATED_BY</t>
-  </si>
-  <si>
     <t>HAS_APPLICATION_IMPLICATIONS</t>
   </si>
   <si>
@@ -98,9 +89,6 @@
     <t>REQUIRES</t>
   </si>
   <si>
-    <t>IS_REQUIRED_BY</t>
-  </si>
-  <si>
     <t>Skill_Type</t>
   </si>
   <si>
@@ -147,6 +135,39 @@
   </si>
   <si>
     <t>Time_Based_Conceptual_Business_Event</t>
+  </si>
+  <si>
+    <t>DEFINED_BY</t>
+  </si>
+  <si>
+    <t>Business_Capability_Chain</t>
+  </si>
+  <si>
+    <t>DEFINES</t>
+  </si>
+  <si>
+    <t>USES</t>
+  </si>
+  <si>
+    <t>USED_BY</t>
+  </si>
+  <si>
+    <t>SUPPORTED_BY</t>
+  </si>
+  <si>
+    <t>SUPERSEDED_BY</t>
+  </si>
+  <si>
+    <t>MOTIVATED_BY</t>
+  </si>
+  <si>
+    <t>REQUIRED_BY</t>
+  </si>
+  <si>
+    <t>Business_Capability_Chain_Type</t>
+  </si>
+  <si>
+    <t>Conceptual_Business_Model</t>
   </si>
 </sst>
 </file>
@@ -479,8 +500,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E30" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E30" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E36" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E36" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -809,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -824,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -833,7 +854,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -841,7 +862,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -850,7 +871,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -858,16 +879,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -875,16 +896,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -892,16 +913,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -909,50 +930,50 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>12</v>
-      </c>
       <c r="D8" s="8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -960,24 +981,24 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>4</v>
@@ -986,41 +1007,41 @@
         <v>5</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1028,24 +1049,24 @@
         <v>3</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>4</v>
@@ -1054,126 +1075,126 @@
         <v>3</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>19</v>
-      </c>
       <c r="D15" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="D17" s="8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1181,152 +1202,254 @@
         <v>5</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="E29" s="9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>16</v>
+      <c r="D33" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4755D47A-C37D-4FD6-A4C3-7EA226D62775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A3F5C6-2C45-4831-8239-FEBB0D6DB78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11460" yWindow="1125" windowWidth="16200" windowHeight="14325" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
   <si>
     <t>source</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>Conceptual_Business_Model</t>
+  </si>
+  <si>
+    <t>Value_Stream</t>
+  </si>
+  <si>
+    <t>Value_Stage</t>
   </si>
 </sst>
 </file>
@@ -500,8 +506,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E36" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E36" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E42" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E42" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -830,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -1449,6 +1455,108 @@
         <v>43</v>
       </c>
       <c r="E36" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>13</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A3F5C6-2C45-4831-8239-FEBB0D6DB78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DC34DA-FF6B-49F7-A9D0-8BA30333E715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="54">
   <si>
     <t>source</t>
   </si>
@@ -174,6 +174,30 @@
   </si>
   <si>
     <t>Value_Stage</t>
+  </si>
+  <si>
+    <t>Business_Role</t>
+  </si>
+  <si>
+    <t>Business_Logical</t>
+  </si>
+  <si>
+    <t>REALIZES</t>
+  </si>
+  <si>
+    <t>REALIZED_BY</t>
+  </si>
+  <si>
+    <t>TRIGGERS</t>
+  </si>
+  <si>
+    <t>PARTICIPATES</t>
+  </si>
+  <si>
+    <t>TRIGGERED_BY</t>
+  </si>
+  <si>
+    <t>PARTICIPATED_BY</t>
   </si>
 </sst>
 </file>
@@ -506,8 +530,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E42" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E42" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E52" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E52" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -836,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -1558,6 +1582,176 @@
       </c>
       <c r="E42" s="8" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DC34DA-FF6B-49F7-A9D0-8BA30333E715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DEAC2F-052C-439E-950A-9F7879AECDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="58">
   <si>
     <t>source</t>
   </si>
@@ -198,6 +198,18 @@
   </si>
   <si>
     <t>PARTICIPATED_BY</t>
+  </si>
+  <si>
+    <t>Business_Event</t>
+  </si>
+  <si>
+    <t>External_Business_Event</t>
+  </si>
+  <si>
+    <t>Time_Based_Business_Event</t>
+  </si>
+  <si>
+    <t>RAISED_BY</t>
   </si>
 </sst>
 </file>
@@ -530,8 +542,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E52" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E52" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E59" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E59" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -860,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -1751,6 +1763,125 @@
         <v>46</v>
       </c>
       <c r="E52" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E59" s="8" t="s">
         <v>47</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DEAC2F-052C-439E-950A-9F7879AECDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A16A243-0F75-4A3A-9910-D16FAF1CF713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="62">
   <si>
     <t>source</t>
   </si>
@@ -210,6 +210,18 @@
   </si>
   <si>
     <t>RAISED_BY</t>
+  </si>
+  <si>
+    <t>Product_Type</t>
+  </si>
+  <si>
+    <t>INSTANCES</t>
+  </si>
+  <si>
+    <t>INSTANCE_OF</t>
+  </si>
+  <si>
+    <t>Product</t>
   </si>
 </sst>
 </file>
@@ -542,8 +554,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E59" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E59" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E65" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E65" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -872,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -1882,6 +1894,108 @@
         <v>46</v>
       </c>
       <c r="E59" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="9" t="s">
         <v>47</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A16A243-0F75-4A3A-9910-D16FAF1CF713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0113F59C-BEE2-470D-BC18-24CDC51D054D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="64">
   <si>
     <t>source</t>
   </si>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>Product</t>
+  </si>
+  <si>
+    <t>Business_Process_Type</t>
+  </si>
+  <si>
+    <t>Business_Process_Family</t>
   </si>
 </sst>
 </file>
@@ -554,8 +560,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E65" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E65" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E69" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E69" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -884,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -1996,6 +2002,74 @@
         <v>58</v>
       </c>
       <c r="E65" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>47</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0113F59C-BEE2-470D-BC18-24CDC51D054D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADBEEC8-6AA8-49C9-AF97-BFC6506AC282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="72">
   <si>
     <t>source</t>
   </si>
@@ -228,6 +228,30 @@
   </si>
   <si>
     <t>Business_Process_Family</t>
+  </si>
+  <si>
+    <t>PRODUCES</t>
+  </si>
+  <si>
+    <t>PRODUCED_BY</t>
+  </si>
+  <si>
+    <t>OWNS</t>
+  </si>
+  <si>
+    <t>PERFORMS</t>
+  </si>
+  <si>
+    <t>OWNED_BY</t>
+  </si>
+  <si>
+    <t>PERFORMED_BY</t>
+  </si>
+  <si>
+    <t>OPERATES_AT</t>
+  </si>
+  <si>
+    <t>Site_Category</t>
   </si>
 </sst>
 </file>
@@ -560,8 +584,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E69" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E69" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E76" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E76" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -890,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -2070,6 +2094,125 @@
         <v>62</v>
       </c>
       <c r="E69" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E71" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E76" s="9" t="s">
         <v>47</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ADBEEC8-6AA8-49C9-AF97-BFC6506AC282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640E65D5-FCA3-44F1-BE77-EC35BB5A218D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="75">
   <si>
     <t>source</t>
   </si>
@@ -252,6 +252,15 @@
   </si>
   <si>
     <t>Site_Category</t>
+  </si>
+  <si>
+    <t>Business_Process</t>
+  </si>
+  <si>
+    <t>Business_Activity</t>
+  </si>
+  <si>
+    <t>Business_Task</t>
   </si>
 </sst>
 </file>
@@ -584,8 +593,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E76" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E76" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E83" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E83" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -914,7 +923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -2144,8 +2153,8 @@
       <c r="D72" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E72" s="7" t="s">
-        <v>62</v>
+      <c r="E72" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2161,16 +2170,16 @@
       <c r="D73" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E73" s="7" t="s">
-        <v>62</v>
+      <c r="E73" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>62</v>
+      <c r="B74" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>68</v>
@@ -2186,8 +2195,8 @@
       <c r="A75" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B75" s="7" t="s">
-        <v>62</v>
+      <c r="B75" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>69</v>
@@ -2213,6 +2222,125 @@
         <v>71</v>
       </c>
       <c r="E76" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E83" s="8" t="s">
         <v>47</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640E65D5-FCA3-44F1-BE77-EC35BB5A218D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEADA34-D8C3-4E1B-8711-79CED4CD11B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="81">
   <si>
     <t>source</t>
   </si>
@@ -261,6 +261,24 @@
   </si>
   <si>
     <t>Business_Task</t>
+  </si>
+  <si>
+    <t>Physical_Process</t>
+  </si>
+  <si>
+    <t>Business_Physical</t>
+  </si>
+  <si>
+    <t>IMPLEMENTS</t>
+  </si>
+  <si>
+    <t>IMPLEMENTED_BY</t>
+  </si>
+  <si>
+    <t>Physical_Activities</t>
+  </si>
+  <si>
+    <t>Physical_Process_Type</t>
   </si>
 </sst>
 </file>
@@ -593,8 +611,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E83" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E83" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E89" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E89" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -923,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -2341,6 +2359,108 @@
         <v>72</v>
       </c>
       <c r="E83" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E89" s="9" t="s">
         <v>47</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEADA34-D8C3-4E1B-8711-79CED4CD11B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2586A7CC-ED5D-444F-A566-0C2B53E914EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="14025" yWindow="870" windowWidth="14385" windowHeight="12060" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="90">
   <si>
     <t>source</t>
   </si>
@@ -279,6 +279,33 @@
   </si>
   <si>
     <t>Physical_Process_Type</t>
+  </si>
+  <si>
+    <t>ACTOR_TO_ROLE_RELATION</t>
+  </si>
+  <si>
+    <t>Business_Relationship</t>
+  </si>
+  <si>
+    <t>act_to_role_to_role</t>
+  </si>
+  <si>
+    <t>bus_role_played_by_actor</t>
+  </si>
+  <si>
+    <t>Actor</t>
+  </si>
+  <si>
+    <t>act_to_role_from_actor</t>
+  </si>
+  <si>
+    <t>actor_plays_role</t>
+  </si>
+  <si>
+    <t>STAKEHOLDER_OF</t>
+  </si>
+  <si>
+    <t>STAKEHOLDERS</t>
   </si>
 </sst>
 </file>
@@ -611,8 +638,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E89" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E89" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E95" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E95" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -941,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -2462,6 +2489,108 @@
       </c>
       <c r="E89" s="9" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2586A7CC-ED5D-444F-A566-0C2B53E914EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E200FB7D-7F48-46DC-8C7D-8EB54E4123A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14025" yWindow="870" windowWidth="14385" windowHeight="12060" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="90">
   <si>
     <t>source</t>
   </si>
@@ -638,8 +638,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E95" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E95" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E103" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E103" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -968,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -2591,6 +2591,142 @@
       </c>
       <c r="E95" s="9" t="s">
         <v>82</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E200FB7D-7F48-46DC-8C7D-8EB54E4123A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1E723A-511F-484D-A5AA-EE10DF4BA5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="94">
   <si>
     <t>source</t>
   </si>
@@ -306,6 +306,18 @@
   </si>
   <si>
     <t>STAKEHOLDERS</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>PERFORMED_AT</t>
+  </si>
+  <si>
+    <t>Geographic_Location</t>
+  </si>
+  <si>
+    <t>Utilities</t>
   </si>
 </sst>
 </file>
@@ -638,8 +650,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E103" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E103" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E111" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E111" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -968,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -2726,6 +2738,142 @@
         <v>79</v>
       </c>
       <c r="E103" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E110" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E111" s="9" t="s">
         <v>76</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1E723A-511F-484D-A5AA-EE10DF4BA5F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47672AF7-CA2D-4C25-B3DD-88BB15FD73FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="14730" yWindow="870" windowWidth="13680" windowHeight="12060" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="97">
   <si>
     <t>source</t>
   </si>
@@ -318,6 +318,15 @@
   </si>
   <si>
     <t>Utilities</t>
+  </si>
+  <si>
+    <t>BASES_AT</t>
+  </si>
+  <si>
+    <t>Group_Actor</t>
+  </si>
+  <si>
+    <t>Individual_Actor</t>
   </si>
 </sst>
 </file>
@@ -650,8 +659,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E111" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E111" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E116" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E116" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -980,7 +989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -2874,6 +2883,91 @@
         <v>90</v>
       </c>
       <c r="E111" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E113" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="E114" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E115" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E116" s="8" t="s">
         <v>76</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47672AF7-CA2D-4C25-B3DD-88BB15FD73FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90446B6-A200-4800-8B1F-F15CAED2643C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14730" yWindow="870" windowWidth="13680" windowHeight="12060" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="16830" yWindow="870" windowWidth="11580" windowHeight="12060" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="101">
   <si>
     <t>source</t>
   </si>
@@ -327,6 +327,18 @@
   </si>
   <si>
     <t>Individual_Actor</t>
+  </si>
+  <si>
+    <t>Application_Provider</t>
+  </si>
+  <si>
+    <t>Application_Logical</t>
+  </si>
+  <si>
+    <t>APP_PRO_TO_PHYS_BUS_RELATION</t>
+  </si>
+  <si>
+    <t>Application_Relationship</t>
   </si>
 </sst>
 </file>
@@ -659,8 +671,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E116" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E116" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E120" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E120" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -989,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -2969,6 +2981,74 @@
       </c>
       <c r="E116" s="8" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E119" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90446B6-A200-4800-8B1F-F15CAED2643C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01639243-DF0B-470E-AB5A-1E5E36408659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16830" yWindow="870" windowWidth="11580" windowHeight="12060" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="16140" yWindow="195" windowWidth="12150" windowHeight="15585" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="104">
   <si>
     <t>source</t>
   </si>
@@ -339,6 +339,15 @@
   </si>
   <si>
     <t>Application_Relationship</t>
+  </si>
+  <si>
+    <t>FROM</t>
+  </si>
+  <si>
+    <t>FOR</t>
+  </si>
+  <si>
+    <t>Application_Architecture_Objective</t>
   </si>
 </sst>
 </file>
@@ -485,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -496,6 +505,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -671,8 +681,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E120" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E120" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E124" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E124" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1001,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -3049,6 +3059,74 @@
       </c>
       <c r="E120" s="8" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D121" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E121" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E124" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC6D450-D209-461E-86B3-31278F7212D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEDD92FD-17BE-4A9C-95DF-91751A87A043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="110">
   <si>
     <t>source</t>
   </si>
@@ -65,9 +65,6 @@
     <t>MOTIVATES</t>
   </si>
   <si>
-    <t>HAS_APPLICATION_IMPLICATIONS</t>
-  </si>
-  <si>
     <t>Application_Driver</t>
   </si>
   <si>
@@ -360,6 +357,15 @@
   </si>
   <si>
     <t>Technology_Conceptual</t>
+  </si>
+  <si>
+    <t>IMPLICATED_BY</t>
+  </si>
+  <si>
+    <t>Information_Driver</t>
+  </si>
+  <si>
+    <t>Technology_Driver</t>
   </si>
 </sst>
 </file>
@@ -521,7 +527,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="9">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -636,6 +642,22 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
@@ -650,22 +672,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
         <top/>
         <bottom/>
         <vertical style="thin">
@@ -674,22 +680,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -708,8 +698,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E134" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E134" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E144" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E144" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1038,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -1053,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
@@ -1062,7 +1052,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1070,7 +1060,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -1079,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1087,16 +1077,16 @@
         <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1104,7 +1094,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>6</v>
@@ -1113,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1121,16 +1111,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1138,16 +1128,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1155,7 +1145,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
@@ -1164,296 +1154,296 @@
         <v>5</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="9" t="s">
         <v>14</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
+      <c r="E9" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>13</v>
+      <c r="A12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>13</v>
+        <v>37</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>13</v>
+      <c r="E13" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>3</v>
+      <c r="D14" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>13</v>
+      <c r="A15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="D16" s="8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>20</v>
+      <c r="B18" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>13</v>
+      <c r="A19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>15</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>15</v>
+      <c r="A24" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1461,390 +1451,390 @@
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>38</v>
+        <v>12</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="D27" s="8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>13</v>
+      <c r="A28" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>31</v>
-      </c>
       <c r="E29" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="D30" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="9" t="s">
-        <v>13</v>
+      <c r="D31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>13</v>
+      <c r="D32" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>13</v>
+      <c r="A33" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E33" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="E34" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>13</v>
+      <c r="B36" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D36" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="E37" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>13</v>
+        <v>44</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>13</v>
+      <c r="A41" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>12</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>13</v>
+        <v>40</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>13</v>
+        <v>47</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D43" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>13</v>
+      <c r="D43" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="8" t="s">
+      <c r="A44" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D44" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>47</v>
+      <c r="D44" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="5" t="s">
+      <c r="A45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>13</v>
+      <c r="E45" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C46" s="8" t="s">
+      <c r="A46" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>13</v>
+      <c r="D46" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="5" t="s">
+      <c r="B47" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>13</v>
+      <c r="D47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -1852,24 +1842,24 @@
         <v>45</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>13</v>
+        <v>46</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>50</v>
@@ -1878,58 +1868,58 @@
         <v>44</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>47</v>
+      <c r="A50" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>13</v>
+      <c r="E50" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="5" t="s">
+      <c r="B51" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C52" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D52" s="7" t="s">
-        <v>46</v>
-      </c>
       <c r="E52" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1937,254 +1927,254 @@
         <v>55</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D54" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>54</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C55" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D55" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>47</v>
+      <c r="B56" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>47</v>
+        <v>56</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>13</v>
+      <c r="A57" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>47</v>
+      <c r="A58" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B59" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="D59" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>47</v>
+        <v>23</v>
+      </c>
+      <c r="E59" s="9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>47</v>
+        <v>23</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="9" t="s">
-        <v>13</v>
+        <v>57</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="9" t="s">
-        <v>13</v>
+        <v>57</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D61" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E62" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E61" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D63" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>47</v>
+      <c r="A64" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D64" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E64" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E64" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B65" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="E65" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D66" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>47</v>
+        <v>61</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="E67" s="8" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2192,152 +2182,152 @@
         <v>62</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>47</v>
+        <v>61</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B69" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D69" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>47</v>
+      <c r="D69" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D70" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>47</v>
+      <c r="D70" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C71" s="8" t="s">
+      <c r="A71" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D71" s="8" t="s">
-        <v>62</v>
+      <c r="D71" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C72" s="5" t="s">
+      <c r="A72" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>66</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C73" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D73" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>47</v>
+      <c r="D73" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C74" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>47</v>
+      <c r="D74" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E74" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>47</v>
+        <v>26</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2345,16 +2335,16 @@
         <v>72</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2362,279 +2352,279 @@
         <v>73</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B79" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="D79" s="7" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>49</v>
+      <c r="A81" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>47</v>
+      <c r="A82" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>39</v>
+        <v>75</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>75</v>
+        <v>26</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D87" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="E87" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87" s="8" t="s">
+      <c r="D88" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E88" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E87" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="8" t="s">
-        <v>80</v>
-      </c>
       <c r="B89" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>47</v>
+        <v>82</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>83</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C91" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D91" s="7" t="s">
-        <v>81</v>
-      </c>
       <c r="E91" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="7" t="s">
-        <v>81</v>
+      <c r="A92" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E92" s="8" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="8" t="s">
-        <v>85</v>
+      <c r="A93" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>87</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="7" t="s">
-        <v>81</v>
+      <c r="A94" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>88</v>
@@ -2642,348 +2632,348 @@
       <c r="D94" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E94" s="8" t="s">
-        <v>76</v>
+      <c r="E94" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D96" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D95" s="8" t="s">
+      <c r="E96" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E95" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="7" t="s">
-        <v>75</v>
+      <c r="A97" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D97" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B98" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E97" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="C98" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E99" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D99" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E99" s="9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D100" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E100" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E100" s="6" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>76</v>
+      <c r="A101" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D101" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B102" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E101" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>82</v>
-      </c>
       <c r="C102" s="8" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>79</v>
+        <v>58</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="7" t="s">
-        <v>71</v>
+      <c r="A104" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="B105" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>60</v>
+      <c r="A105" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E105" s="9" t="s">
-        <v>47</v>
+        <v>89</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>76</v>
+      <c r="A106" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B107" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D107" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>76</v>
+      <c r="D107" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D108" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E108" s="6" t="s">
-        <v>76</v>
+      <c r="D108" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E108" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C109" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D109" s="8" t="s">
-        <v>90</v>
-      </c>
       <c r="E109" s="9" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="B110" s="8" t="s">
-        <v>76</v>
+        <v>91</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B111" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C111" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C111" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E111" s="9" t="s">
-        <v>76</v>
+      <c r="D111" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D112" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>76</v>
+      <c r="D113" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B114" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="E114" s="9" t="s">
-        <v>82</v>
+        <v>26</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2991,16 +2981,16 @@
         <v>95</v>
       </c>
       <c r="B115" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -3008,203 +2998,203 @@
         <v>96</v>
       </c>
       <c r="B116" s="8" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>76</v>
+        <v>4</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E116" s="9" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="E117" s="9" t="s">
-        <v>100</v>
+        <v>79</v>
+      </c>
+      <c r="E117" s="8" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E118" s="8" t="s">
         <v>99</v>
-      </c>
-      <c r="B118" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D118" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B119" s="8" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E119" s="8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="7" t="s">
-        <v>99</v>
+        <v>22</v>
       </c>
       <c r="B120" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D120" s="7" t="s">
-        <v>97</v>
+      <c r="D120" s="8" t="s">
+        <v>102</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>98</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="B121" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D121" s="8" t="s">
-        <v>103</v>
+      <c r="D121" s="7" t="s">
+        <v>22</v>
       </c>
       <c r="E121" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B122" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C122" s="8" t="s">
+      <c r="B124" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D122" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B123" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E123" s="5" t="s">
+      <c r="E124" s="8" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D124" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E124" s="9" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B125" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C125" s="8" t="s">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>103</v>
       </c>
       <c r="E125" s="8" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B126" s="8" t="s">
-        <v>14</v>
+      <c r="A126" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="C126" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E126" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D126" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E126" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>6</v>
-      </c>
       <c r="D127" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E127" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -3212,118 +3202,288 @@
         <v>103</v>
       </c>
       <c r="B128" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D128" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E128" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D129" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E128" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
+      <c r="E129" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B129" s="8" t="s">
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="B130" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C130" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E129" s="9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D130" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E131" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D131" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="7" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E132" s="8" t="s">
-        <v>107</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="B133" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="E133" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>14</v>
+      <c r="A134" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D134" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>14</v>
+        <v>107</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E144" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEDD92FD-17BE-4A9C-95DF-91751A87A043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C80945F-FA73-4EBC-A838-FAEB68CDFD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="113">
   <si>
     <t>source</t>
   </si>
@@ -366,6 +366,15 @@
   </si>
   <si>
     <t>Technology_Driver</t>
+  </si>
+  <si>
+    <t>Application_Architecture_Principle</t>
+  </si>
+  <si>
+    <t>RELEVANT_TO</t>
+  </si>
+  <si>
+    <t>RELEVANT_FROM</t>
   </si>
 </sst>
 </file>
@@ -698,8 +707,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E144" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E144" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E148" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E148" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1028,7 +1037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -3484,6 +3493,74 @@
       </c>
       <c r="E144" s="9" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E148" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C80945F-FA73-4EBC-A838-FAEB68CDFD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89D8386-13B6-4412-B0D7-5873583C6286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="117">
   <si>
     <t>source</t>
   </si>
@@ -375,6 +375,18 @@
   </si>
   <si>
     <t>RELEVANT_FROM</t>
+  </si>
+  <si>
+    <t>Application_Service</t>
+  </si>
+  <si>
+    <t>Composite_Application_Service</t>
+  </si>
+  <si>
+    <t>COMPOSES</t>
+  </si>
+  <si>
+    <t>COMPOSED_OF</t>
   </si>
 </sst>
 </file>
@@ -707,8 +719,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E148" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E148" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E152" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E152" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1037,7 +1049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -3561,6 +3573,74 @@
       </c>
       <c r="E148" s="9" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D4FE88F-3E95-49CE-8AE1-0F70521876AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0F14A8-0C39-433D-975F-73701E75A017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="60" windowWidth="17790" windowHeight="14805" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="125">
   <si>
     <t>source</t>
   </si>
@@ -405,6 +405,12 @@
   </si>
   <si>
     <t>Composite_Application_Provider</t>
+  </si>
+  <si>
+    <t>PROVIDED_BY</t>
+  </si>
+  <si>
+    <t>Application_Provider_Role</t>
   </si>
 </sst>
 </file>
@@ -774,8 +780,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E168" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E168" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E175" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E175" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1104,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -3967,6 +3973,125 @@
         <v>95</v>
       </c>
       <c r="E168" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E169" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E170" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E171" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E172" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E173" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B174" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E174" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E175" s="9" t="s">
         <v>96</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{431C87EB-E84B-4537-B396-69680F2DD79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95EEE15-BA8C-438F-8F53-D8A0C9BD157B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11670" yWindow="0" windowWidth="17115" windowHeight="15585" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="3780" yWindow="3015" windowWidth="19740" windowHeight="11295" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="132">
   <si>
     <t>source</t>
   </si>
@@ -411,6 +411,27 @@
   </si>
   <si>
     <t>Application_Provider_Role</t>
+  </si>
+  <si>
+    <t>Static_Application_Provider_Architecture</t>
+  </si>
+  <si>
+    <t>:APA-STATIC-RELATION</t>
+  </si>
+  <si>
+    <t>:Application_Relationship</t>
+  </si>
+  <si>
+    <t>Logical Software Architecture</t>
+  </si>
+  <si>
+    <t>SCA RELATION</t>
+  </si>
+  <si>
+    <t>Application_Function_Implementation</t>
+  </si>
+  <si>
+    <t>Application_Function</t>
   </si>
 </sst>
 </file>
@@ -780,8 +801,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E177" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E177" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E189" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E189" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1110,13 +1131,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
     <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.5703125" customWidth="1"/>
+    <col min="4" max="4" width="37.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4126,6 +4147,210 @@
         <v>124</v>
       </c>
       <c r="E177" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E178" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="E184" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E189" s="9" t="s">
         <v>96</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDF7237-2B8E-4064-85AF-2C22E341D1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EAE006-E89D-4168-87DE-154EFF34265D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="8505" yWindow="480" windowWidth="19740" windowHeight="14940" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="136">
   <si>
     <t>source</t>
   </si>
@@ -438,6 +438,12 @@
   </si>
   <si>
     <t>Dynamic_Application_Provider_Architecture</t>
+  </si>
+  <si>
+    <t>Static_Application_Service_Architecture</t>
+  </si>
+  <si>
+    <t>:ASU-TO-ASU-STATIC-RELATION</t>
   </si>
 </sst>
 </file>
@@ -807,8 +813,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E195" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E195" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E199" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E199" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1137,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -4459,6 +4465,74 @@
         <v>112</v>
       </c>
       <c r="E195" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D198" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="E199" s="9" t="s">
         <v>96</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA6080C-A11F-40CE-AC5D-21B6E213A53D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F7B116-4E94-42B3-BE71-51C2D02E9E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="153">
   <si>
     <t>source</t>
   </si>
@@ -489,6 +489,12 @@
   </si>
   <si>
     <t>DELIVERED_BY</t>
+  </si>
+  <si>
+    <t>Technology_Product_Role</t>
+  </si>
+  <si>
+    <t>RUNTIME_ON</t>
   </si>
 </sst>
 </file>
@@ -669,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -683,8 +689,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -860,8 +864,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E219" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E219" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E222" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E222" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1190,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E219"/>
+  <dimension ref="A1:E222"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -4890,36 +4894,87 @@
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A218" s="14" t="s">
+      <c r="A218" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B218" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C218" s="14" t="s">
+      <c r="B218" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C218" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D218" s="14" t="s">
+      <c r="D218" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E218" s="14" t="s">
+      <c r="E218" s="5" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A219" s="13" t="s">
+      <c r="A219" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B219" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C219" s="14" t="s">
+      <c r="B219" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C219" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D219" s="13" t="s">
+      <c r="D219" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="E219" s="13" t="s">
+      <c r="E219" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B220" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C220" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D220" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E220" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C221" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D221" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E221" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C222" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D222" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E222" s="9" t="s">
         <v>96</v>
       </c>
     </row>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C4015D-D7D6-4B43-BA98-03A58746721D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA6F91E-2247-4A0A-9033-509BE6257A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="160">
   <si>
     <t>source</t>
   </si>
@@ -885,8 +885,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E230" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E230" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E232" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E232" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1215,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E232"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -5133,6 +5133,40 @@
       </c>
       <c r="E230" s="8" t="s">
         <v>140</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B231" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C231" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E231" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B232" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C232" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D232" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E232" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/graphdb_inputs/meta-model.xlsx
+++ b/graphdb_inputs/meta-model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\EA_MetaModel\graphdb_inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B54892E-7504-4ECF-BBEE-218E16A23BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2375A651-3730-4A2B-BB8B-F2514C524667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
+    <workbookView xWindow="9420" yWindow="30" windowWidth="19335" windowHeight="15165" xr2:uid="{8170F98D-87F3-4BBF-AF33-E74360046B09}"/>
   </bookViews>
   <sheets>
     <sheet name="meta-model" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="163">
   <si>
     <t>source</t>
   </si>
@@ -519,6 +519,12 @@
   </si>
   <si>
     <t>Software_Information_Representation_Usage</t>
+  </si>
+  <si>
+    <t>Technology_Provider_Role</t>
+  </si>
+  <si>
+    <t>Technology_Product_Build_Role</t>
   </si>
 </sst>
 </file>
@@ -888,8 +894,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E236" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="A1:E236" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}" name="Table1" displayName="Table1" ref="A1:E242" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E242" xr:uid="{AB3976EA-2B8D-46CC-B8F3-0DB3881E99F9}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{768FEF15-CE91-4610-9962-A2388F3D8C76}" name="source" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6BA5C30C-3AC2-4B96-8F4B-FB5D1FBD553E}" name="source_label" dataDxfId="3"/>
@@ -1218,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C6A4DC-C1A5-4591-B4CB-A04A3C9852DB}">
-  <dimension ref="A1:E236"/>
+  <dimension ref="A1:E242"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.7109375" customWidth="1"/>
@@ -5238,6 +5244,108 @@
       </c>
       <c r="E236" s="9" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B237" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C237" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D237" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B238" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C238" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D238" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E238" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D239" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D240" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E240" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C241" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E241" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="B242" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C242" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D242" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E242" s="9" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
